--- a/РАБОЧИЙ СТОЛ/расчет Останкино КИ/машины Останкино КИ и ЗПФ.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчет Останкино КИ/машины Останкино КИ и ЗПФ.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет Останкино КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00E91E3-0649-4F69-81D1-BEF1C2DEFE1E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFEDD3DB-FF25-47EA-A43F-30DED6BC00D2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Доброцен-Донецк</t>
   </si>
@@ -66,15 +66,6 @@
     <t>ОБЩИИЙ ВЕС</t>
   </si>
   <si>
-    <t>1 машина</t>
-  </si>
-  <si>
-    <t>2 машина</t>
-  </si>
-  <si>
-    <t>3 машина</t>
-  </si>
-  <si>
     <t>Остаток</t>
   </si>
   <si>
@@ -94,6 +85,18 @@
   </si>
   <si>
     <t>Мелитополь ЗПФ</t>
+  </si>
+  <si>
+    <t>САП 11,07</t>
+  </si>
+  <si>
+    <t>САП 12,07</t>
+  </si>
+  <si>
+    <t>САП 13,07</t>
+  </si>
+  <si>
+    <t>с Крымом</t>
   </si>
 </sst>
 </file>
@@ -124,7 +127,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -134,6 +137,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -223,13 +232,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -519,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -536,16 +547,16 @@
         <v>10</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -557,7 +568,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2">
-        <f>B2-C2-D2-E2</f>
+        <f t="shared" ref="F2:F14" si="0">B2-C2-D2-E2</f>
         <v>0</v>
       </c>
     </row>
@@ -570,7 +581,7 @@
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2">
-        <f t="shared" ref="F3:F4" si="0">B3-C3-D3-E3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -578,9 +589,13 @@
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="2">
+        <v>2222</v>
+      </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2">
+        <v>2222</v>
+      </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2">
         <f t="shared" si="0"/>
@@ -591,25 +606,31 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="2">
+        <v>5610</v>
+      </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="E5" s="6">
+        <v>5610</v>
+      </c>
       <c r="F5" s="2">
-        <f t="shared" ref="F5:F14" si="1">B5-C5-D5-E5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -617,25 +638,35 @@
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" s="2">
+        <v>9306</v>
+      </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="D7" s="2">
+        <v>5200</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4106</v>
+      </c>
       <c r="F7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="B8" s="2">
+        <v>64</v>
+      </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="D8" s="2">
+        <v>64</v>
+      </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -643,25 +674,33 @@
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="2"/>
+      <c r="B9" s="2">
+        <v>5971</v>
+      </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="E9" s="2">
+        <v>5971</v>
+      </c>
       <c r="F9" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="2"/>
+        <v>16</v>
+      </c>
+      <c r="B10" s="2">
+        <v>371</v>
+      </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="E10" s="2">
+        <v>371</v>
+      </c>
       <c r="F10" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -669,25 +708,31 @@
       <c r="A11" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="B11" s="2">
+        <v>2030</v>
+      </c>
+      <c r="C11" s="6">
+        <v>2030</v>
+      </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -700,7 +745,7 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -713,29 +758,29 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4">
         <f>SUM(B2:B14)</f>
-        <v>0</v>
+        <v>25574</v>
       </c>
       <c r="C15" s="4">
         <f>SUM(C2:C14)</f>
-        <v>0</v>
+        <v>2030</v>
       </c>
       <c r="D15" s="4">
         <f>SUM(D2:D14)</f>
-        <v>0</v>
+        <v>7486</v>
       </c>
       <c r="E15" s="4">
         <f>SUM(E2:E14)</f>
-        <v>0</v>
+        <v>16058</v>
       </c>
       <c r="F15" s="4">
         <f>SUM(F2:F14)</f>
@@ -743,25 +788,30 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="17" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="8"/>
-    </row>
-    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="9"/>
+      <c r="E17" s="10"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C18" s="3">
         <f>IF(ROUNDUP(C15/500,0)&gt;32,32,ROUNDUP(C15/500,0))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D18" s="3">
-        <f t="shared" ref="D18:E18" si="2">IF(ROUNDUP(D15/500,0)&gt;32,32,ROUNDUP(D15/500,0))</f>
-        <v>0</v>
+        <f t="shared" ref="D18:E18" si="1">IF(ROUNDUP(D15/500,0)&gt;32,32,ROUNDUP(D15/500,0))</f>
+        <v>15</v>
       </c>
       <c r="E18" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
